--- a/Team-Data/2007-08/2-14-2007-08.xlsx
+++ b/Team-Data/2007-08/2-14-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -790,10 +857,10 @@
         <v>16</v>
       </c>
       <c r="AU2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW2" t="n">
         <v>8</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1203,7 @@
         <v>15</v>
       </c>
       <c r="AO4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
         <v>14</v>
@@ -1160,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="AW4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX4" t="n">
         <v>12</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
         <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>0.404</v>
+        <v>0.392</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1231,13 +1298,13 @@
         <v>0.424</v>
       </c>
       <c r="L5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M5" t="n">
         <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.345</v>
+        <v>0.347</v>
       </c>
       <c r="O5" t="n">
         <v>18.1</v>
@@ -1246,16 +1313,16 @@
         <v>24.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="R5" t="n">
         <v>13.5</v>
       </c>
       <c r="S5" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="T5" t="n">
-        <v>43.6</v>
+        <v>43.4</v>
       </c>
       <c r="U5" t="n">
         <v>21.2</v>
@@ -1273,31 +1340,31 @@
         <v>5.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.7</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.8</v>
+        <v>-3</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF5" t="n">
         <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI5" t="n">
         <v>25</v>
@@ -1330,19 +1397,19 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT5" t="n">
         <v>7</v>
       </c>
       <c r="AU5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV5" t="n">
         <v>13</v>
       </c>
       <c r="AW5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX5" t="n">
         <v>14</v>
@@ -1351,13 +1418,13 @@
         <v>27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" t="n">
         <v>35</v>
       </c>
       <c r="F7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G7" t="n">
-        <v>0.66</v>
+        <v>0.673</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
@@ -1589,10 +1656,10 @@
         <v>36.3</v>
       </c>
       <c r="J7" t="n">
-        <v>78.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L7" t="n">
         <v>5.7</v>
@@ -1601,28 +1668,28 @@
         <v>16.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.339</v>
+        <v>0.337</v>
       </c>
       <c r="O7" t="n">
         <v>21</v>
       </c>
       <c r="P7" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="R7" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="S7" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T7" t="n">
         <v>42.5</v>
       </c>
       <c r="U7" t="n">
-        <v>19.9</v>
+        <v>20.2</v>
       </c>
       <c r="V7" t="n">
         <v>12.6</v>
@@ -1646,28 +1713,28 @@
         <v>99.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE7" t="n">
         <v>5</v>
       </c>
       <c r="AF7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
         <v>15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AK7" t="n">
         <v>6</v>
@@ -1679,7 +1746,7 @@
         <v>19</v>
       </c>
       <c r="AN7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AO7" t="n">
         <v>8</v>
@@ -1691,7 +1758,7 @@
         <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
         <v>8</v>
@@ -1700,7 +1767,7 @@
         <v>9</v>
       </c>
       <c r="AU7" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AV7" t="n">
         <v>4</v>
@@ -1715,7 +1782,7 @@
         <v>5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE8" t="n">
         <v>10</v>
@@ -1861,7 +1928,7 @@
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1897,7 +1964,7 @@
         <v>20</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA8" t="n">
         <v>2</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>2.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
         <v>10</v>
@@ -2240,7 +2307,7 @@
         <v>9</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT10" t="n">
         <v>14</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE11" t="n">
         <v>10</v>
@@ -2407,7 +2474,7 @@
         <v>9</v>
       </c>
       <c r="AN11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO11" t="n">
         <v>27</v>
@@ -2431,7 +2498,7 @@
         <v>11</v>
       </c>
       <c r="AV11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
         <v>15</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -2568,10 +2635,10 @@
         <v>22</v>
       </c>
       <c r="AG12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>6.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2965,7 +3032,7 @@
         <v>14</v>
       </c>
       <c r="AR14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
@@ -2977,7 +3044,7 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW14" t="n">
         <v>6</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-4.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,7 +3184,7 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI15" t="n">
         <v>10</v>
@@ -3156,7 +3223,7 @@
         <v>18</v>
       </c>
       <c r="AU15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV15" t="n">
         <v>29</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E16" t="n">
         <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G16" t="n">
-        <v>0.173</v>
+        <v>0.176</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
@@ -3233,37 +3300,37 @@
         <v>0.454</v>
       </c>
       <c r="L16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M16" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0.335</v>
+        <v>0.33</v>
       </c>
       <c r="O16" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P16" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.718</v>
+        <v>0.72</v>
       </c>
       <c r="R16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="T16" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="U16" t="n">
         <v>20.1</v>
       </c>
       <c r="V16" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W16" t="n">
         <v>7.3</v>
@@ -3278,16 +3345,16 @@
         <v>20.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>93</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC16" t="n">
         <v>-7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3299,7 +3366,7 @@
         <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI16" t="n">
         <v>26</v>
@@ -3317,10 +3384,10 @@
         <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AO16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP16" t="n">
         <v>16</v>
@@ -3332,16 +3399,16 @@
         <v>29</v>
       </c>
       <c r="AS16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT16" t="n">
         <v>30</v>
       </c>
       <c r="AU16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW16" t="n">
         <v>19</v>
@@ -3356,7 +3423,7 @@
         <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB16" t="n">
         <v>30</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3566,7 @@
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO17" t="n">
         <v>26</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-7.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3681,7 +3748,7 @@
         <v>22</v>
       </c>
       <c r="AN18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3696,7 +3763,7 @@
         <v>7</v>
       </c>
       <c r="AS18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT18" t="n">
         <v>13</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3930,7 @@
         <v>20</v>
       </c>
       <c r="AN19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -4015,10 +4082,10 @@
         <v>5.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF20" t="n">
         <v>3</v>
@@ -4090,7 +4157,7 @@
         <v>8</v>
       </c>
       <c r="BC20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-5.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4209,7 +4276,7 @@
         <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI21" t="n">
         <v>28</v>
@@ -4227,7 +4294,7 @@
         <v>17</v>
       </c>
       <c r="AN21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO21" t="n">
         <v>13</v>
@@ -4269,7 +4336,7 @@
         <v>16</v>
       </c>
       <c r="BB21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC21" t="n">
         <v>26</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4464,7 @@
         <v>11</v>
       </c>
       <c r="AJ22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK22" t="n">
         <v>5</v>
@@ -4430,7 +4497,7 @@
         <v>11</v>
       </c>
       <c r="AU22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV22" t="n">
         <v>12</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -4606,13 +4673,13 @@
         <v>3</v>
       </c>
       <c r="AS23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT23" t="n">
         <v>15</v>
       </c>
       <c r="AU23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV23" t="n">
         <v>22</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E24" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F24" t="n">
         <v>16</v>
       </c>
       <c r="G24" t="n">
-        <v>0.698</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
@@ -4683,40 +4750,40 @@
         <v>41.5</v>
       </c>
       <c r="J24" t="n">
-        <v>84.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="K24" t="n">
-        <v>0.493</v>
+        <v>0.492</v>
       </c>
       <c r="L24" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="M24" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="N24" t="n">
         <v>0.383</v>
       </c>
       <c r="O24" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P24" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.796</v>
+        <v>0.795</v>
       </c>
       <c r="R24" t="n">
         <v>8.5</v>
       </c>
       <c r="S24" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T24" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="U24" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="V24" t="n">
         <v>13.8</v>
@@ -4731,7 +4798,7 @@
         <v>3.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA24" t="n">
         <v>20.1</v>
@@ -4740,10 +4807,10 @@
         <v>109.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4755,7 +4822,7 @@
         <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI24" t="n">
         <v>1</v>
@@ -4776,7 +4843,7 @@
         <v>3</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
         <v>25</v>
@@ -4791,7 +4858,7 @@
         <v>6</v>
       </c>
       <c r="AT24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4800,7 +4867,7 @@
         <v>8</v>
       </c>
       <c r="AW24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX24" t="n">
         <v>2</v>
@@ -4812,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="BA24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BB24" t="n">
         <v>2</v>
       </c>
       <c r="BC24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-0.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="n">
         <v>17</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>4.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE27" t="n">
         <v>7</v>
@@ -5298,7 +5365,7 @@
         <v>5</v>
       </c>
       <c r="AG27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH27" t="n">
         <v>22</v>
@@ -5307,7 +5374,7 @@
         <v>21</v>
       </c>
       <c r="AJ27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK27" t="n">
         <v>11</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-7.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE28" t="n">
         <v>28</v>
@@ -5501,7 +5568,7 @@
         <v>26</v>
       </c>
       <c r="AN28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO28" t="n">
         <v>24</v>
@@ -5537,7 +5604,7 @@
         <v>23</v>
       </c>
       <c r="AZ28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA28" t="n">
         <v>26</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>3.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5914,7 @@
         <v>8</v>
       </c>
       <c r="AH30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI30" t="n">
         <v>3</v>
@@ -5883,7 +5950,7 @@
         <v>26</v>
       </c>
       <c r="AT30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU30" t="n">
         <v>2</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
@@ -6086,7 +6153,7 @@
         <v>5</v>
       </c>
       <c r="BA31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
         <v>14</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-14-2007-08</t>
+          <t>2008-02-14</t>
         </is>
       </c>
     </row>
